--- a/database/scraped_market_data.xlsx
+++ b/database/scraped_market_data.xlsx
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12 12:59:32</t>
+          <t>2026-06-13 05:22:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
